--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_los_lagos.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_los_lagos.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.86802889734671</v>
+      </c>
+      <c r="C2">
         <v>23.67867810474469</v>
-      </c>
-      <c r="C2">
-        <v>27.86802889734671</v>
       </c>
       <c r="D2">
         <v>4.22320872633351</v>
       </c>
       <c r="E2">
-        <v>15.62467345754858</v>
+        <v>18.38906925042068</v>
       </c>
       <c r="F2">
         <v>65.98625729203074</v>
       </c>
       <c r="G2">
-        <v>18.38906925042068</v>
+        <v>15.62467345754858</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>27.3234046093685</v>
+      </c>
+      <c r="C3">
         <v>33.58848489891006</v>
-      </c>
-      <c r="C3">
-        <v>27.3234046093685</v>
       </c>
       <c r="D3">
         <v>2.977210800099083</v>
       </c>
       <c r="E3">
-        <v>20.87383660806618</v>
+        <v>16.98035160289556</v>
       </c>
       <c r="F3">
         <v>62.14581178903826</v>
       </c>
       <c r="G3">
-        <v>16.98035160289556</v>
+        <v>20.87383660806618</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>25.49399457574584</v>
+      </c>
+      <c r="C4">
         <v>46.76481983727238</v>
-      </c>
-      <c r="C4">
-        <v>25.49399457574584</v>
       </c>
       <c r="D4">
         <v>2.138359569179785</v>
       </c>
       <c r="E4">
-        <v>27.14799820062978</v>
+        <v>14.79982006297796</v>
       </c>
       <c r="F4">
         <v>58.05218173639226</v>
       </c>
       <c r="G4">
-        <v>14.79982006297796</v>
+        <v>27.14799820062978</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>26.2898049864231</v>
+      </c>
+      <c r="C5">
         <v>41.6316958775611</v>
-      </c>
-      <c r="C5">
-        <v>26.2898049864231</v>
       </c>
       <c r="D5">
         <v>2.402016009487103</v>
       </c>
       <c r="E5">
-        <v>24.79235575156193</v>
+        <v>15.65600882028666</v>
       </c>
       <c r="F5">
         <v>59.55163542815142</v>
       </c>
       <c r="G5">
-        <v>15.65600882028666</v>
+        <v>24.79235575156193</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>31.16040032458751</v>
+      </c>
+      <c r="C6">
         <v>31.45793886935353</v>
-      </c>
-      <c r="C6">
-        <v>31.16040032458751</v>
       </c>
       <c r="D6">
         <v>3.178847807394669</v>
       </c>
       <c r="E6">
-        <v>19.34464404524284</v>
+        <v>19.16167664670659</v>
       </c>
       <c r="F6">
         <v>61.49367930805057</v>
       </c>
       <c r="G6">
-        <v>19.16167664670659</v>
+        <v>19.34464404524284</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>27.74505494505495</v>
+      </c>
+      <c r="C7">
         <v>39.93846153846154</v>
-      </c>
-      <c r="C7">
-        <v>27.74505494505495</v>
       </c>
       <c r="D7">
         <v>2.503852080123266</v>
       </c>
       <c r="E7">
-        <v>23.81776239907728</v>
+        <v>16.54608367411135</v>
       </c>
       <c r="F7">
         <v>59.63615392681137</v>
       </c>
       <c r="G7">
-        <v>16.54608367411135</v>
+        <v>23.81776239907728</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>26.80860983759422</v>
+      </c>
+      <c r="C8">
         <v>32.88522806744891</v>
-      </c>
-      <c r="C8">
-        <v>26.80860983759422</v>
       </c>
       <c r="D8">
         <v>3.040879017013232</v>
       </c>
       <c r="E8">
-        <v>20.59267188944577</v>
+        <v>16.78750425770035</v>
       </c>
       <c r="F8">
         <v>62.61982385285388</v>
       </c>
       <c r="G8">
-        <v>16.78750425770035</v>
+        <v>20.59267188944577</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>24.72205376996159</v>
+      </c>
+      <c r="C9">
         <v>43.11704063068527</v>
-      </c>
-      <c r="C9">
-        <v>24.72205376996159</v>
       </c>
       <c r="D9">
         <v>2.319268635724332</v>
       </c>
       <c r="E9">
+        <v>14.72961580151753</v>
+      </c>
+      <c r="F9">
+        <v>59.58087438275323</v>
+      </c>
+      <c r="G9">
         <v>25.68950981572926</v>
-      </c>
-      <c r="F9">
-        <v>59.58087438275322</v>
-      </c>
-      <c r="G9">
-        <v>14.72961580151752</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.27265074187099</v>
+      </c>
+      <c r="C10">
         <v>26.55214142902241</v>
-      </c>
-      <c r="C10">
-        <v>28.27265074187099</v>
       </c>
       <c r="D10">
         <v>3.766174576439116</v>
       </c>
       <c r="E10">
-        <v>17.14979949704343</v>
+        <v>18.26106164616326</v>
       </c>
       <c r="F10">
         <v>64.58913885679331</v>
       </c>
       <c r="G10">
-        <v>18.26106164616326</v>
+        <v>17.14979949704343</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>24.40724082403243</v>
+      </c>
+      <c r="C11">
         <v>26.02032317174746</v>
-      </c>
-      <c r="C11">
-        <v>24.40724082403243</v>
       </c>
       <c r="D11">
         <v>3.84314980793854</v>
       </c>
       <c r="E11">
-        <v>17.297576641258</v>
+        <v>16.22524501208911</v>
       </c>
       <c r="F11">
-        <v>66.47717834665288</v>
+        <v>66.47717834665289</v>
       </c>
       <c r="G11">
-        <v>16.22524501208911</v>
+        <v>17.29757664125801</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>24.15235944608641</v>
+      </c>
+      <c r="C12">
         <v>34.91183209909342</v>
-      </c>
-      <c r="C12">
-        <v>24.15235944608641</v>
       </c>
       <c r="D12">
         <v>2.864358413392942</v>
       </c>
       <c r="E12">
-        <v>21.94826614334329</v>
+        <v>15.18403306958391</v>
       </c>
       <c r="F12">
         <v>62.8677007870728</v>
       </c>
       <c r="G12">
-        <v>15.18403306958391</v>
+        <v>21.94826614334329</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>24.74492059267146</v>
+      </c>
+      <c r="C13">
         <v>29.11010558069382</v>
-      </c>
-      <c r="C13">
-        <v>24.74492059267146</v>
       </c>
       <c r="D13">
         <v>3.435233160621762</v>
       </c>
       <c r="E13">
-        <v>18.92047748111413</v>
+        <v>16.08327086096534</v>
       </c>
       <c r="F13">
         <v>64.99625165792054</v>
       </c>
       <c r="G13">
-        <v>16.08327086096534</v>
+        <v>18.92047748111413</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>25.28644804425129</v>
+      </c>
+      <c r="C14">
         <v>36.9814302647175</v>
-      </c>
-      <c r="C14">
-        <v>25.28644804425129</v>
       </c>
       <c r="D14">
         <v>2.704059829059829</v>
       </c>
       <c r="E14">
-        <v>22.79035792549305</v>
+        <v>15.58315071828586</v>
       </c>
       <c r="F14">
-        <v>61.62649135622107</v>
+        <v>61.62649135622109</v>
       </c>
       <c r="G14">
-        <v>15.58315071828585</v>
+        <v>22.79035792549306</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>27.19068676112264</v>
+      </c>
+      <c r="C15">
         <v>27.41629816803538</v>
-      </c>
-      <c r="C15">
-        <v>27.19068676112264</v>
       </c>
       <c r="D15">
         <v>3.647465437788018</v>
       </c>
       <c r="E15">
-        <v>17.73289750175111</v>
+        <v>17.58697174877422</v>
       </c>
       <c r="F15">
         <v>64.68013074947467</v>
       </c>
       <c r="G15">
-        <v>17.58697174877422</v>
+        <v>17.73289750175111</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>23.18059299191374</v>
+      </c>
+      <c r="C16">
         <v>39.23758182518291</v>
-      </c>
-      <c r="C16">
-        <v>23.18059299191374</v>
       </c>
       <c r="D16">
         <v>2.548577036310108</v>
       </c>
       <c r="E16">
-        <v>24.158368895211</v>
+        <v>14.27216690374585</v>
       </c>
       <c r="F16">
         <v>61.56946420104315</v>
       </c>
       <c r="G16">
-        <v>14.27216690374585</v>
+        <v>24.158368895211</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>25.19747235387046</v>
+      </c>
+      <c r="C17">
         <v>34.88678251711427</v>
-      </c>
-      <c r="C17">
-        <v>25.19747235387046</v>
       </c>
       <c r="D17">
         <v>2.866415094339623</v>
       </c>
       <c r="E17">
-        <v>21.79276315789473</v>
+        <v>15.74013157894737</v>
       </c>
       <c r="F17">
         <v>62.46710526315788</v>
       </c>
       <c r="G17">
-        <v>15.74013157894737</v>
+        <v>21.79276315789473</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>27.97124971017853</v>
+      </c>
+      <c r="C18">
         <v>21.21029445861349</v>
-      </c>
-      <c r="C18">
-        <v>27.97124971017853</v>
       </c>
       <c r="D18">
         <v>4.714691735898557</v>
       </c>
       <c r="E18">
-        <v>14.21777377140903</v>
+        <v>18.74980572565354</v>
       </c>
       <c r="F18">
         <v>67.03242050293743</v>
       </c>
       <c r="G18">
-        <v>18.74980572565354</v>
+        <v>14.21777377140903</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>23.07827307827308</v>
+      </c>
+      <c r="C19">
         <v>38.76798876798877</v>
-      </c>
-      <c r="C19">
-        <v>23.07827307827308</v>
       </c>
       <c r="D19">
         <v>2.579447713897691</v>
       </c>
       <c r="E19">
-        <v>23.95358924311429</v>
+        <v>14.25937974409022</v>
       </c>
       <c r="F19">
         <v>61.7870310127955</v>
       </c>
       <c r="G19">
-        <v>14.25937974409022</v>
+        <v>23.95358924311429</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>22.46580475922803</v>
+      </c>
+      <c r="C20">
         <v>37.53044781712573</v>
-      </c>
-      <c r="C20">
-        <v>22.46580475922803</v>
       </c>
       <c r="D20">
         <v>2.664503245132301</v>
       </c>
       <c r="E20">
-        <v>23.45707928328844</v>
+        <v>14.04145684506383</v>
       </c>
       <c r="F20">
         <v>62.50146387164774</v>
       </c>
       <c r="G20">
-        <v>14.04145684506383</v>
+        <v>23.45707928328844</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>25.73802949454413</v>
+      </c>
+      <c r="C21">
         <v>31.75946231499321</v>
-      </c>
-      <c r="C21">
-        <v>25.73802949454413</v>
       </c>
       <c r="D21">
         <v>3.148667915350424</v>
       </c>
       <c r="E21">
-        <v>20.16505910671906</v>
+        <v>16.34186627280978</v>
       </c>
       <c r="F21">
         <v>63.49307462047116</v>
       </c>
       <c r="G21">
-        <v>16.34186627280978</v>
+        <v>20.16505910671906</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>27.77221108884436</v>
+      </c>
+      <c r="C22">
         <v>37.4248496993988</v>
-      </c>
-      <c r="C22">
-        <v>27.77221108884436</v>
       </c>
       <c r="D22">
         <v>2.672021419009371</v>
       </c>
       <c r="E22">
-        <v>22.65467044076021</v>
+        <v>16.81156490093005</v>
       </c>
       <c r="F22">
         <v>60.53376465830974</v>
       </c>
       <c r="G22">
-        <v>16.81156490093005</v>
+        <v>22.65467044076021</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>27.40115223739247</v>
+      </c>
+      <c r="C23">
         <v>41.96196038197459</v>
-      </c>
-      <c r="C23">
-        <v>27.40115223739247</v>
       </c>
       <c r="D23">
         <v>2.383110776753809</v>
       </c>
       <c r="E23">
-        <v>24.77632805219013</v>
+        <v>16.17893755824791</v>
       </c>
       <c r="F23">
         <v>59.04473438956197</v>
       </c>
       <c r="G23">
-        <v>16.17893755824791</v>
+        <v>24.77632805219013</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>23.92979452054794</v>
+      </c>
+      <c r="C24">
         <v>36.06592465753425</v>
-      </c>
-      <c r="C24">
-        <v>23.92979452054794</v>
       </c>
       <c r="D24">
         <v>2.772700296735905</v>
       </c>
       <c r="E24">
-        <v>22.54180602006689</v>
+        <v>14.95652173913043</v>
       </c>
       <c r="F24">
         <v>62.50167224080268</v>
       </c>
       <c r="G24">
-        <v>14.95652173913043</v>
+        <v>22.54180602006689</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>24.97262864536678</v>
+      </c>
+      <c r="C25">
         <v>41.02717229023589</v>
-      </c>
-      <c r="C25">
-        <v>24.97262864536678</v>
       </c>
       <c r="D25">
         <v>2.437409024745269</v>
       </c>
       <c r="E25">
-        <v>24.71519366830555</v>
+        <v>15.04377023623936</v>
       </c>
       <c r="F25">
         <v>60.24103609545509</v>
       </c>
       <c r="G25">
-        <v>15.04377023623936</v>
+        <v>24.71519366830555</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>24.81324449828387</v>
+      </c>
+      <c r="C26">
         <v>47.58732081566727</v>
-      </c>
-      <c r="C26">
-        <v>24.81324449828387</v>
       </c>
       <c r="D26">
         <v>2.101400084853628</v>
       </c>
       <c r="E26">
+        <v>14.39278604051997</v>
+      </c>
+      <c r="F26">
+        <v>58.00445016980912</v>
+      </c>
+      <c r="G26">
         <v>27.60276378967092</v>
-      </c>
-      <c r="F26">
-        <v>58.00445016980911</v>
-      </c>
-      <c r="G26">
-        <v>14.39278604051997</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>23.79237551223147</v>
+      </c>
+      <c r="C27">
         <v>40.49422575437725</v>
-      </c>
-      <c r="C27">
-        <v>23.79237551223147</v>
       </c>
       <c r="D27">
         <v>2.469487887151181</v>
       </c>
       <c r="E27">
-        <v>24.6485260770975</v>
+        <v>14.48223733938019</v>
       </c>
       <c r="F27">
         <v>60.86923658352229</v>
       </c>
       <c r="G27">
-        <v>14.48223733938019</v>
+        <v>24.6485260770975</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>24.68394437420986</v>
+      </c>
+      <c r="C28">
         <v>33.43868520859672</v>
-      </c>
-      <c r="C28">
-        <v>24.68394437420986</v>
       </c>
       <c r="D28">
         <v>2.99054820415879</v>
       </c>
       <c r="E28">
-        <v>21.14731161303218</v>
+        <v>15.6106336198281</v>
       </c>
       <c r="F28">
         <v>63.24205476713971</v>
       </c>
       <c r="G28">
-        <v>15.6106336198281</v>
+        <v>21.14731161303218</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>30.93306288032454</v>
+      </c>
+      <c r="C29">
         <v>33.41784989858012</v>
-      </c>
-      <c r="C29">
-        <v>30.93306288032454</v>
       </c>
       <c r="D29">
         <v>2.992412746585736</v>
       </c>
       <c r="E29">
-        <v>20.33323048441839</v>
+        <v>18.82135143474236</v>
       </c>
       <c r="F29">
         <v>60.84541808083925</v>
       </c>
       <c r="G29">
-        <v>18.82135143474236</v>
+        <v>20.33323048441839</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>23.83804192162479</v>
+      </c>
+      <c r="C30">
         <v>28.21247233433147</v>
-      </c>
-      <c r="C30">
-        <v>23.83804192162479</v>
       </c>
       <c r="D30">
         <v>3.544531610521458</v>
       </c>
       <c r="E30">
+        <v>15.67771213288809</v>
+      </c>
+      <c r="F30">
+        <v>65.76761709050432</v>
+      </c>
+      <c r="G30">
         <v>18.55467077660759</v>
-      </c>
-      <c r="F30">
-        <v>65.76761709050433</v>
-      </c>
-      <c r="G30">
-        <v>15.67771213288809</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>23.20341047503045</v>
+      </c>
+      <c r="C31">
         <v>34.16565164433617</v>
-      </c>
-      <c r="C31">
-        <v>23.20341047503045</v>
       </c>
       <c r="D31">
         <v>2.926916221033868</v>
       </c>
       <c r="E31">
-        <v>21.71052631578947</v>
+        <v>14.74458204334365</v>
       </c>
       <c r="F31">
         <v>63.54489164086688</v>
       </c>
       <c r="G31">
-        <v>14.74458204334365</v>
+        <v>21.71052631578947</v>
       </c>
     </row>
   </sheetData>
